--- a/artfynd/A 58485-2025 artfynd.xlsx
+++ b/artfynd/A 58485-2025 artfynd.xlsx
@@ -898,6 +898,16 @@
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars Karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars Karlsson</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 58485-2025 artfynd.xlsx
+++ b/artfynd/A 58485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129821831</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58485-2025 artfynd.xlsx
+++ b/artfynd/A 58485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129821831</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58485-2025 artfynd.xlsx
+++ b/artfynd/A 58485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129821831</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58485-2025 artfynd.xlsx
+++ b/artfynd/A 58485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129821831</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58485-2025 artfynd.xlsx
+++ b/artfynd/A 58485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129821831</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58485-2025 artfynd.xlsx
+++ b/artfynd/A 58485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129821831</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58485-2025 artfynd.xlsx
+++ b/artfynd/A 58485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129821831</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58485-2025 artfynd.xlsx
+++ b/artfynd/A 58485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129821831</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58485-2025 artfynd.xlsx
+++ b/artfynd/A 58485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129821831</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58485-2025 artfynd.xlsx
+++ b/artfynd/A 58485-2025 artfynd.xlsx
@@ -675,62 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62000526</v>
+        <v>129821831</v>
       </c>
       <c r="B2" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ambrickalandet, norr om Svedden, Upl</t>
+          <t>Ambricka, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632069.0301289503</v>
+        <v>632031</v>
       </c>
       <c r="R2" t="n">
-        <v>6711791.208271491</v>
+        <v>6711829</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-05-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-05-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca 75 rosetter på olika platser inom 50 m radie.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,72 +771,77 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre blåbärstallskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Lars Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Lars Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129821831</v>
+        <v>62000526</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>106329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221423</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ambricka, Upl</t>
+          <t>Ambrickalandet, norr om Svedden, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632031</v>
+        <v>632069</v>
       </c>
       <c r="R3" t="n">
-        <v>6711829</v>
+        <v>6711791</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,17 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2016-05-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca 75 rosetter på olika platser inom 50 m radie.</t>
+          <t>2016-05-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,20 +882,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Äldre blåbärstallskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Karlsson</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Karlsson</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 58485-2025 artfynd.xlsx
+++ b/artfynd/A 58485-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129821831</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000526</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>